--- a/evals/datasets/document_extraction/files/DOC-113.xlsx
+++ b/evals/datasets/document_extraction/files/DOC-113.xlsx
@@ -413,41 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Material Clinico Levante S.L. | Invoice INV-44149 | 2026-09-11</t>
+          <t>INV-44149 | Invoice | Material Clinico Levante S.L. | 2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Order PO-0018 | EUR</t>
+          <t>Order | PO-0018 | Currency | EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>| Item | Qty | Unit | Total |</t>
+          <t>code | qty | unit price | amount</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>| GLV-LTX-M | 50 | 6.42 | 321.00 |</t>
+          <t>GLV-LTX-M | 50 | 6.42 | 321.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>| FORCEPS-DISP | 10 | 14.90 | 149.00 |</t>
+          <t>FORCEPS-DISP | 10 | 14.90 | 149.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>| TOTAL | 470.00 |</t>
         </is>
       </c>
     </row>
